--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D154</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Ross River virus infection</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>罗斯河病毒感染</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>217</v>
       </c>
-      <c r="N2" t="n">
-        <v>49</v>
-      </c>
       <c r="O2" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.7970001648357945</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -690,97 +864,126 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>D154</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Ross River virus infection</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>罗斯河病毒感染</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>257</v>
       </c>
-      <c r="N3" t="n">
-        <v>58.03225806451614</v>
-      </c>
       <c r="O3" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.9439126376165859</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -809,97 +1012,126 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>D154</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Ross River virus infection</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>罗斯河病毒感染</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>270</v>
       </c>
-      <c r="N4" t="n">
-        <v>67.5</v>
-      </c>
       <c r="O4" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.9916591912703433</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -928,97 +1160,126 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>D154</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Ross River virus infection</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>罗斯河病毒感染</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>314</v>
       </c>
-      <c r="N5" t="n">
-        <v>70.90322580645162</v>
-      </c>
       <c r="O5" t="n">
+        <v>314</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>1.153262911329214</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -1047,97 +1308,126 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>D154</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Ross River virus infection</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>罗斯河病毒感染</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>259</v>
       </c>
-      <c r="N6" t="n">
-        <v>60.43333333333333</v>
-      </c>
       <c r="O6" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.9512582612556257</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -1166,97 +1456,126 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>D154</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Ross River virus infection</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>罗斯河病毒感染</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>166</v>
       </c>
-      <c r="N7" t="n">
-        <v>37.48387096774194</v>
-      </c>
       <c r="O7" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.6096867620402852</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -1285,97 +1604,126 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>D154</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Ross River virus infection</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>罗斯河病毒感染</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>78</v>
-      </c>
       <c r="N8" t="n">
-        <v>18.2</v>
+        <v>85</v>
       </c>
       <c r="O8" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
-        <v>0.2864793219225436</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="n">
+        <v>0.3121890046591821</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -1404,97 +1752,126 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>AU</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>D154</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Ross River virus infection</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>罗斯河病毒感染</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="R9" t="n">
+        <v>0.03305530637567811</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -1612,7 +1989,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1622,27 +1999,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1561</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1652,22 +2029,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1796,16 +1796,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03305530637567811</v>
+        <v>0.0367281181951979</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O7" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6096867620402852</v>
+        <v>0.613359573859805</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1796,16 +1796,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0367281181951979</v>
+        <v>0.04040093001471769</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>314</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>1.153262911329214</v>
       </c>
@@ -1357,9 +1354,6 @@
       <c r="O6" t="n">
         <v>259</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.9512582612556257</v>
       </c>
@@ -1505,9 +1499,6 @@
       <c r="O7" t="n">
         <v>167</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.613359573859805</v>
       </c>
@@ -1653,9 +1644,6 @@
       <c r="O8" t="n">
         <v>85</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.3121890046591821</v>
       </c>
@@ -1800,9 +1788,6 @@
       </c>
       <c r="O9" t="n">
         <v>11</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.04040093001471769</v>

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O8" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3121890046591821</v>
+        <v>0.3195346282982217</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04040093001471769</v>
+        <v>0.05141936547327706</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1580</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O7" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R7" t="n">
-        <v>0.613359573859805</v>
+        <v>0.6170323856793247</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05141936547327706</v>
+        <v>0.05876498911231665</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1585</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05876498911231665</v>
+        <v>0.06978342457087601</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1588</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="O8" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3195346282982217</v>
+        <v>0.3415714992153405</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
-        <v>0.06978342457087601</v>
+        <v>0.1028387309465541</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1591</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1028387309465541</v>
+        <v>0.1101843545855937</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1606</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1101843545855937</v>
+        <v>0.1138571664051135</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="O9" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1138571664051135</v>
+        <v>0.1542580964198312</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1609</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O7" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6170323856793247</v>
+        <v>0.6207051974988445</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1542580964198312</v>
+        <v>0.1469124727807916</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="O9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1469124727807916</v>
+        <v>0.157930908239351</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1619</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -1600,12 +1600,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1630,26 +1630,23 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>93</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3415714992153405</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1683,12 +1680,12 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1703,12 +1700,12 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -1745,12 +1742,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1775,26 +1772,23 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.157930908239351</v>
+        <v>24</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1828,35 +1822,3168 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>11</v>
+      </c>
+      <c r="O10" t="n">
+        <v>11</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>97</v>
+      </c>
+      <c r="O11" t="n">
+        <v>97</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>21</v>
+      </c>
+      <c r="O15" t="n">
+        <v>21</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>96</v>
+      </c>
+      <c r="O16" t="n">
+        <v>96</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3525899346738999</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BB16" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>24</v>
+      </c>
+      <c r="O18" t="n">
+        <v>24</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>48</v>
+      </c>
+      <c r="O20" t="n">
+        <v>48</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>9</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>58</v>
+      </c>
+      <c r="O24" t="n">
+        <v>58</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.2130230855321478</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>11</v>
+      </c>
+      <c r="O26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>32</v>
+      </c>
+      <c r="O27" t="n">
+        <v>32</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ross-river-virus-infection</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ross River virus infection</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>罗斯河病毒感染</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -1895,7 +5022,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1978,7 +5105,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -1988,7 +5115,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -2040,7 +5167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1622</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d154/2026-2029.xlsx
+++ b/diseases/d154/2026-2029.xlsx
@@ -3914,13 +3914,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O24" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2130230855321478</v>
+        <v>0.2203687091711874</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.01101843545855937</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1946</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="16">
